--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123283245</v>
+        <v>123282276</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488616</v>
+        <v>488614</v>
       </c>
       <c r="R2" t="n">
-        <v>6845834</v>
+        <v>6845651</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283290</v>
+        <v>123283182</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488669</v>
+        <v>488622</v>
       </c>
       <c r="R3" t="n">
-        <v>6845859</v>
+        <v>6845865</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123282344</v>
+        <v>123282046</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488613</v>
+        <v>488627</v>
       </c>
       <c r="R4" t="n">
-        <v>6845644</v>
+        <v>6845653</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282365</v>
+        <v>123285070</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>98282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488621</v>
+        <v>488727</v>
       </c>
       <c r="R5" t="n">
-        <v>6845654</v>
+        <v>6845511</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123281886</v>
+        <v>123284387</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488542</v>
+        <v>488840</v>
       </c>
       <c r="R6" t="n">
-        <v>6845601</v>
+        <v>6845500</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285070</v>
+        <v>123281886</v>
       </c>
       <c r="B7" t="n">
-        <v>98282</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488727</v>
+        <v>488542</v>
       </c>
       <c r="R7" t="n">
-        <v>6845511</v>
+        <v>6845601</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282046</v>
+        <v>123283290</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488627</v>
+        <v>488669</v>
       </c>
       <c r="R8" t="n">
-        <v>6845653</v>
+        <v>6845859</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,19 +1377,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123282094</v>
+        <v>123284651</v>
       </c>
       <c r="B9" t="n">
         <v>79848</v>
@@ -1430,17 +1425,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488580</v>
+        <v>488778</v>
       </c>
       <c r="R9" t="n">
-        <v>6845622</v>
+        <v>6845534</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123284651</v>
+        <v>123281923</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,37 +1507,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488778</v>
+        <v>488566</v>
       </c>
       <c r="R10" t="n">
-        <v>6845534</v>
+        <v>6845601</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123281923</v>
+        <v>123283234</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488566</v>
+        <v>488645</v>
       </c>
       <c r="R11" t="n">
-        <v>6845601</v>
+        <v>6845868</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123283234</v>
+        <v>123282646</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>78845</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488645</v>
+        <v>488667</v>
       </c>
       <c r="R12" t="n">
-        <v>6845868</v>
+        <v>6845634</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123282276</v>
+        <v>123281905</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488614</v>
+        <v>488550</v>
       </c>
       <c r="R13" t="n">
-        <v>6845651</v>
+        <v>6845607</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123283182</v>
+        <v>123282126</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488622</v>
+        <v>488580</v>
       </c>
       <c r="R14" t="n">
-        <v>6845865</v>
+        <v>6845622</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123282646</v>
+        <v>123282365</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488621</v>
       </c>
       <c r="R15" t="n">
-        <v>6845634</v>
+        <v>6845654</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282126</v>
+        <v>123282344</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R16" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2189,6 +2179,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123284387</v>
+        <v>123283245</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2251,17 +2246,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488840</v>
+        <v>488616</v>
       </c>
       <c r="R17" t="n">
-        <v>6845500</v>
+        <v>6845834</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2300,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123281905</v>
+        <v>123282094</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488550</v>
+        <v>488580</v>
       </c>
       <c r="R18" t="n">
-        <v>6845607</v>
+        <v>6845622</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2393,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123282276</v>
+        <v>123282094</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>79851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488614</v>
+        <v>488580</v>
       </c>
       <c r="R2" t="n">
-        <v>6845651</v>
+        <v>6845622</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283182</v>
+        <v>123282365</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488622</v>
+        <v>488621</v>
       </c>
       <c r="R3" t="n">
-        <v>6845865</v>
+        <v>6845654</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123282046</v>
+        <v>123283290</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488627</v>
+        <v>488669</v>
       </c>
       <c r="R4" t="n">
-        <v>6845653</v>
+        <v>6845859</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285070</v>
+        <v>123282344</v>
       </c>
       <c r="B5" t="n">
-        <v>98282</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488727</v>
+        <v>488613</v>
       </c>
       <c r="R5" t="n">
-        <v>6845511</v>
+        <v>6845644</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284387</v>
+        <v>123285070</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488840</v>
+        <v>488727</v>
       </c>
       <c r="R6" t="n">
-        <v>6845500</v>
+        <v>6845511</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123281886</v>
+        <v>123282646</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488542</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6845601</v>
+        <v>6845634</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283290</v>
+        <v>123282046</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488669</v>
+        <v>488627</v>
       </c>
       <c r="R8" t="n">
-        <v>6845859</v>
+        <v>6845653</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123284651</v>
+        <v>123283245</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488778</v>
+        <v>488616</v>
       </c>
       <c r="R9" t="n">
-        <v>6845534</v>
+        <v>6845834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123281923</v>
+        <v>123283182</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,14 +1537,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488566</v>
+        <v>488622</v>
       </c>
       <c r="R10" t="n">
-        <v>6845601</v>
+        <v>6845865</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1596,7 +1606,7 @@
         <v>123283234</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282646</v>
+        <v>123284651</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>79851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488667</v>
+        <v>488778</v>
       </c>
       <c r="R12" t="n">
-        <v>6845634</v>
+        <v>6845534</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281905</v>
+        <v>123281923</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488550</v>
+        <v>488566</v>
       </c>
       <c r="R13" t="n">
-        <v>6845607</v>
+        <v>6845601</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123282126</v>
+        <v>123282276</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488580</v>
+        <v>488614</v>
       </c>
       <c r="R14" t="n">
-        <v>6845622</v>
+        <v>6845651</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123282365</v>
+        <v>123281905</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488621</v>
+        <v>488550</v>
       </c>
       <c r="R15" t="n">
-        <v>6845654</v>
+        <v>6845607</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282344</v>
+        <v>123282126</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488613</v>
+        <v>488580</v>
       </c>
       <c r="R16" t="n">
-        <v>6845644</v>
+        <v>6845622</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2179,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283245</v>
+        <v>123281886</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,37 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488616</v>
+        <v>488542</v>
       </c>
       <c r="R17" t="n">
-        <v>6845834</v>
+        <v>6845601</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2300,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282094</v>
+        <v>123284387</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488580</v>
+        <v>488840</v>
       </c>
       <c r="R18" t="n">
-        <v>6845622</v>
+        <v>6845500</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2388,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123282094</v>
+        <v>123283182</v>
       </c>
       <c r="B2" t="n">
-        <v>79851</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488580</v>
+        <v>488622</v>
       </c>
       <c r="R2" t="n">
-        <v>6845622</v>
+        <v>6845865</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123282365</v>
+        <v>123282646</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>78850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488621</v>
+        <v>488667</v>
       </c>
       <c r="R3" t="n">
-        <v>6845654</v>
+        <v>6845634</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283290</v>
+        <v>123281923</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488669</v>
+        <v>488566</v>
       </c>
       <c r="R4" t="n">
-        <v>6845859</v>
+        <v>6845601</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282344</v>
+        <v>123282365</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488613</v>
+        <v>488621</v>
       </c>
       <c r="R5" t="n">
-        <v>6845644</v>
+        <v>6845654</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285070</v>
+        <v>123283290</v>
       </c>
       <c r="B6" t="n">
-        <v>98285</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488727</v>
+        <v>488669</v>
       </c>
       <c r="R6" t="n">
-        <v>6845511</v>
+        <v>6845859</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282646</v>
+        <v>123283245</v>
       </c>
       <c r="B7" t="n">
-        <v>78848</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488616</v>
       </c>
       <c r="R7" t="n">
-        <v>6845634</v>
+        <v>6845834</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282046</v>
+        <v>123283234</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488627</v>
+        <v>488645</v>
       </c>
       <c r="R8" t="n">
-        <v>6845653</v>
+        <v>6845868</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123283245</v>
+        <v>123282094</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488616</v>
+        <v>488580</v>
       </c>
       <c r="R9" t="n">
-        <v>6845834</v>
+        <v>6845622</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123283182</v>
+        <v>123282276</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>79853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488622</v>
+        <v>488614</v>
       </c>
       <c r="R10" t="n">
-        <v>6845865</v>
+        <v>6845651</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123283234</v>
+        <v>123284651</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488645</v>
+        <v>488778</v>
       </c>
       <c r="R11" t="n">
-        <v>6845868</v>
+        <v>6845534</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123284651</v>
+        <v>123282344</v>
       </c>
       <c r="B12" t="n">
-        <v>79851</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1712,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488778</v>
+        <v>488613</v>
       </c>
       <c r="R12" t="n">
-        <v>6845534</v>
+        <v>6845644</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281923</v>
+        <v>123285070</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>98287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,38 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488566</v>
+        <v>488727</v>
       </c>
       <c r="R13" t="n">
-        <v>6845601</v>
+        <v>6845511</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123282276</v>
+        <v>123281886</v>
       </c>
       <c r="B14" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488614</v>
+        <v>488542</v>
       </c>
       <c r="R14" t="n">
-        <v>6845651</v>
+        <v>6845601</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123281905</v>
+        <v>123284387</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488550</v>
+        <v>488840</v>
       </c>
       <c r="R15" t="n">
-        <v>6845607</v>
+        <v>6845500</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2116,7 +2116,7 @@
         <v>123282126</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123281886</v>
+        <v>123282046</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,17 +2251,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488542</v>
+        <v>488627</v>
       </c>
       <c r="R17" t="n">
-        <v>6845601</v>
+        <v>6845653</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123284387</v>
+        <v>123281905</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488840</v>
+        <v>488550</v>
       </c>
       <c r="R18" t="n">
-        <v>6845500</v>
+        <v>6845607</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123285070</v>
+        <v>123281886</v>
       </c>
       <c r="B13" t="n">
-        <v>98287</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,38 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488727</v>
+        <v>488542</v>
       </c>
       <c r="R13" t="n">
-        <v>6845511</v>
+        <v>6845601</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123281886</v>
+        <v>123285070</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>98287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488542</v>
+        <v>488727</v>
       </c>
       <c r="R14" t="n">
-        <v>6845601</v>
+        <v>6845511</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123283182</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123282646</v>
+        <v>123281886</v>
       </c>
       <c r="B3" t="n">
-        <v>78850</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488667</v>
+        <v>488542</v>
       </c>
       <c r="R3" t="n">
-        <v>6845634</v>
+        <v>6845601</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123281923</v>
+        <v>123284387</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488566</v>
+        <v>488840</v>
       </c>
       <c r="R4" t="n">
-        <v>6845601</v>
+        <v>6845500</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282365</v>
+        <v>123282344</v>
       </c>
       <c r="B5" t="n">
-        <v>79853</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488621</v>
+        <v>488613</v>
       </c>
       <c r="R5" t="n">
-        <v>6845654</v>
+        <v>6845644</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283290</v>
+        <v>123283234</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488669</v>
+        <v>488645</v>
       </c>
       <c r="R6" t="n">
-        <v>6845859</v>
+        <v>6845868</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283245</v>
+        <v>123282046</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488616</v>
+        <v>488627</v>
       </c>
       <c r="R7" t="n">
-        <v>6845834</v>
+        <v>6845653</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283234</v>
+        <v>123282365</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>79854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488645</v>
+        <v>488621</v>
       </c>
       <c r="R8" t="n">
-        <v>6845868</v>
+        <v>6845654</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123282094</v>
+        <v>123281923</v>
       </c>
       <c r="B9" t="n">
-        <v>79853</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488580</v>
+        <v>488566</v>
       </c>
       <c r="R9" t="n">
-        <v>6845622</v>
+        <v>6845601</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,7 +1499,7 @@
         <v>123282276</v>
       </c>
       <c r="B10" t="n">
-        <v>79853</v>
+        <v>79854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123284651</v>
+        <v>123285070</v>
       </c>
       <c r="B11" t="n">
-        <v>79853</v>
+        <v>98293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488778</v>
+        <v>488727</v>
       </c>
       <c r="R11" t="n">
-        <v>6845534</v>
+        <v>6845511</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282344</v>
+        <v>123282094</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>79854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488613</v>
+        <v>488580</v>
       </c>
       <c r="R12" t="n">
-        <v>6845644</v>
+        <v>6845622</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281886</v>
+        <v>123284651</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>79854</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488542</v>
+        <v>488778</v>
       </c>
       <c r="R13" t="n">
-        <v>6845601</v>
+        <v>6845534</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123285070</v>
+        <v>123283290</v>
       </c>
       <c r="B14" t="n">
-        <v>98287</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488727</v>
+        <v>488669</v>
       </c>
       <c r="R14" t="n">
-        <v>6845511</v>
+        <v>6845859</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123284387</v>
+        <v>123281905</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488840</v>
+        <v>488550</v>
       </c>
       <c r="R15" t="n">
-        <v>6845500</v>
+        <v>6845607</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282126</v>
+        <v>123282646</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>78851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488580</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>6845622</v>
+        <v>6845634</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123282046</v>
+        <v>123283245</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488627</v>
+        <v>488616</v>
       </c>
       <c r="R17" t="n">
-        <v>6845653</v>
+        <v>6845834</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123281905</v>
+        <v>123282126</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488550</v>
+        <v>488580</v>
       </c>
       <c r="R18" t="n">
-        <v>6845607</v>
+        <v>6845622</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123283182</v>
+        <v>123282126</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>79856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488622</v>
+        <v>488580</v>
       </c>
       <c r="R2" t="n">
-        <v>6845865</v>
+        <v>6845622</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123281886</v>
+        <v>123283245</v>
       </c>
       <c r="B3" t="n">
-        <v>79853</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488542</v>
+        <v>488616</v>
       </c>
       <c r="R3" t="n">
-        <v>6845601</v>
+        <v>6845834</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123284387</v>
+        <v>123282276</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>79857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488840</v>
+        <v>488614</v>
       </c>
       <c r="R4" t="n">
-        <v>6845500</v>
+        <v>6845651</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282344</v>
+        <v>123284651</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>79857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488613</v>
+        <v>488778</v>
       </c>
       <c r="R5" t="n">
-        <v>6845644</v>
+        <v>6845534</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283234</v>
+        <v>123281923</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488645</v>
+        <v>488566</v>
       </c>
       <c r="R6" t="n">
-        <v>6845868</v>
+        <v>6845601</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282046</v>
+        <v>123285070</v>
       </c>
       <c r="B7" t="n">
-        <v>79853</v>
+        <v>98296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488627</v>
+        <v>488727</v>
       </c>
       <c r="R7" t="n">
-        <v>6845653</v>
+        <v>6845511</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282365</v>
+        <v>123282046</v>
       </c>
       <c r="B8" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488621</v>
+        <v>488627</v>
       </c>
       <c r="R8" t="n">
-        <v>6845654</v>
+        <v>6845653</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123281923</v>
+        <v>123282646</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488566</v>
+        <v>488667</v>
       </c>
       <c r="R9" t="n">
-        <v>6845601</v>
+        <v>6845634</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282276</v>
+        <v>123283290</v>
       </c>
       <c r="B10" t="n">
-        <v>79854</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488614</v>
+        <v>488669</v>
       </c>
       <c r="R10" t="n">
-        <v>6845651</v>
+        <v>6845859</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123285070</v>
+        <v>123282094</v>
       </c>
       <c r="B11" t="n">
-        <v>98293</v>
+        <v>79857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488727</v>
+        <v>488580</v>
       </c>
       <c r="R11" t="n">
-        <v>6845511</v>
+        <v>6845622</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282094</v>
+        <v>123282344</v>
       </c>
       <c r="B12" t="n">
-        <v>79854</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R12" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Tätt beklädd av skrovellav.</t>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123284651</v>
+        <v>123281886</v>
       </c>
       <c r="B13" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488778</v>
+        <v>488542</v>
       </c>
       <c r="R13" t="n">
-        <v>6845534</v>
+        <v>6845601</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123283290</v>
+        <v>123283182</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488669</v>
+        <v>488622</v>
       </c>
       <c r="R14" t="n">
-        <v>6845859</v>
+        <v>6845865</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123281905</v>
+        <v>123284387</v>
       </c>
       <c r="B15" t="n">
-        <v>79853</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488550</v>
+        <v>488840</v>
       </c>
       <c r="R15" t="n">
-        <v>6845607</v>
+        <v>6845500</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282646</v>
+        <v>123281905</v>
       </c>
       <c r="B16" t="n">
-        <v>78851</v>
+        <v>79856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488550</v>
       </c>
       <c r="R16" t="n">
-        <v>6845634</v>
+        <v>6845607</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283245</v>
+        <v>123283234</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>90966</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,37 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488616</v>
+        <v>488645</v>
       </c>
       <c r="R17" t="n">
-        <v>6845834</v>
+        <v>6845868</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282126</v>
+        <v>123282365</v>
       </c>
       <c r="B18" t="n">
-        <v>79853</v>
+        <v>79857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488580</v>
+        <v>488621</v>
       </c>
       <c r="R18" t="n">
-        <v>6845622</v>
+        <v>6845654</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123281923</v>
+        <v>123285070</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>98296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488566</v>
+        <v>488727</v>
       </c>
       <c r="R6" t="n">
-        <v>6845601</v>
+        <v>6845511</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285070</v>
+        <v>123281923</v>
       </c>
       <c r="B7" t="n">
-        <v>98296</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488727</v>
+        <v>488566</v>
       </c>
       <c r="R7" t="n">
-        <v>6845511</v>
+        <v>6845601</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123282126</v>
+        <v>123281886</v>
       </c>
       <c r="B2" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488580</v>
+        <v>488542</v>
       </c>
       <c r="R2" t="n">
-        <v>6845622</v>
+        <v>6845601</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283245</v>
+        <v>123284387</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488616</v>
+        <v>488840</v>
       </c>
       <c r="R3" t="n">
-        <v>6845834</v>
+        <v>6845500</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123282276</v>
+        <v>123281923</v>
       </c>
       <c r="B4" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488614</v>
+        <v>488566</v>
       </c>
       <c r="R4" t="n">
-        <v>6845651</v>
+        <v>6845601</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284651</v>
+        <v>123282365</v>
       </c>
       <c r="B5" t="n">
-        <v>79857</v>
+        <v>79863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488778</v>
+        <v>488621</v>
       </c>
       <c r="R5" t="n">
-        <v>6845534</v>
+        <v>6845654</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285070</v>
+        <v>123284651</v>
       </c>
       <c r="B6" t="n">
-        <v>98296</v>
+        <v>79863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488727</v>
+        <v>488778</v>
       </c>
       <c r="R6" t="n">
-        <v>6845511</v>
+        <v>6845534</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123281923</v>
+        <v>123283182</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488566</v>
+        <v>488622</v>
       </c>
       <c r="R7" t="n">
-        <v>6845601</v>
+        <v>6845865</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1290,7 +1290,7 @@
         <v>123282046</v>
       </c>
       <c r="B8" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123282646</v>
+        <v>123281905</v>
       </c>
       <c r="B9" t="n">
-        <v>78854</v>
+        <v>79862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488667</v>
+        <v>488550</v>
       </c>
       <c r="R9" t="n">
-        <v>6845634</v>
+        <v>6845607</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123283290</v>
+        <v>123282094</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488669</v>
+        <v>488580</v>
       </c>
       <c r="R10" t="n">
-        <v>6845859</v>
+        <v>6845622</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,7 +1601,7 @@
         <v>123282344</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282094</v>
+        <v>123282126</v>
       </c>
       <c r="B12" t="n">
-        <v>79857</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281886</v>
+        <v>123283245</v>
       </c>
       <c r="B13" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488542</v>
+        <v>488616</v>
       </c>
       <c r="R13" t="n">
-        <v>6845601</v>
+        <v>6845834</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123283182</v>
+        <v>123282276</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,34 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488622</v>
+        <v>488614</v>
       </c>
       <c r="R14" t="n">
-        <v>6845865</v>
+        <v>6845651</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123284387</v>
+        <v>123282646</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488840</v>
+        <v>488667</v>
       </c>
       <c r="R15" t="n">
-        <v>6845500</v>
+        <v>6845634</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123281905</v>
+        <v>123285070</v>
       </c>
       <c r="B16" t="n">
-        <v>79856</v>
+        <v>98313</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,38 +2125,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488550</v>
+        <v>488727</v>
       </c>
       <c r="R16" t="n">
-        <v>6845607</v>
+        <v>6845511</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2218,7 +2218,7 @@
         <v>123283234</v>
       </c>
       <c r="B17" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282365</v>
+        <v>123283290</v>
       </c>
       <c r="B18" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488621</v>
+        <v>488669</v>
       </c>
       <c r="R18" t="n">
-        <v>6845654</v>
+        <v>6845859</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282094</v>
+        <v>123282126</v>
       </c>
       <c r="B10" t="n">
-        <v>79863</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282344</v>
+        <v>123282094</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>79863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488613</v>
+        <v>488580</v>
       </c>
       <c r="R11" t="n">
-        <v>6845644</v>
+        <v>6845622</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1678,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282126</v>
+        <v>123282344</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R12" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284651</v>
+        <v>123283182</v>
       </c>
       <c r="B6" t="n">
-        <v>79863</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488778</v>
+        <v>488622</v>
       </c>
       <c r="R6" t="n">
-        <v>6845534</v>
+        <v>6845865</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283182</v>
+        <v>123282046</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>79862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488622</v>
+        <v>488627</v>
       </c>
       <c r="R7" t="n">
-        <v>6845865</v>
+        <v>6845653</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282046</v>
+        <v>123284651</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>79863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488627</v>
+        <v>488778</v>
       </c>
       <c r="R8" t="n">
-        <v>6845653</v>
+        <v>6845534</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282126</v>
+        <v>123282094</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>79863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282094</v>
+        <v>123282344</v>
       </c>
       <c r="B11" t="n">
-        <v>79863</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R11" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Tätt beklädd av skrovellav.</t>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282344</v>
+        <v>123282126</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488613</v>
+        <v>488580</v>
       </c>
       <c r="R12" t="n">
-        <v>6845644</v>
+        <v>6845622</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283182</v>
+        <v>123284651</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>79863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488622</v>
+        <v>488778</v>
       </c>
       <c r="R6" t="n">
-        <v>6845865</v>
+        <v>6845534</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282046</v>
+        <v>123283182</v>
       </c>
       <c r="B7" t="n">
-        <v>79862</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488627</v>
+        <v>488622</v>
       </c>
       <c r="R7" t="n">
-        <v>6845653</v>
+        <v>6845865</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123284651</v>
+        <v>123282046</v>
       </c>
       <c r="B8" t="n">
-        <v>79863</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488778</v>
+        <v>488627</v>
       </c>
       <c r="R8" t="n">
-        <v>6845534</v>
+        <v>6845653</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282094</v>
+        <v>123282126</v>
       </c>
       <c r="B10" t="n">
-        <v>79863</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282344</v>
+        <v>123282094</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>79863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488613</v>
+        <v>488580</v>
       </c>
       <c r="R11" t="n">
-        <v>6845644</v>
+        <v>6845622</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1678,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282126</v>
+        <v>123282344</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R12" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123281886</v>
+        <v>123283290</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488542</v>
+        <v>488669</v>
       </c>
       <c r="R2" t="n">
-        <v>6845601</v>
+        <v>6845859</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284387</v>
+        <v>123283182</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488840</v>
+        <v>488622</v>
       </c>
       <c r="R3" t="n">
-        <v>6845500</v>
+        <v>6845865</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123281923</v>
+        <v>123282365</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>79868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488566</v>
+        <v>488621</v>
       </c>
       <c r="R4" t="n">
-        <v>6845601</v>
+        <v>6845654</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282365</v>
+        <v>123283245</v>
       </c>
       <c r="B5" t="n">
-        <v>79863</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488621</v>
+        <v>488616</v>
       </c>
       <c r="R5" t="n">
-        <v>6845654</v>
+        <v>6845834</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284651</v>
+        <v>123284387</v>
       </c>
       <c r="B6" t="n">
-        <v>79863</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488778</v>
+        <v>488840</v>
       </c>
       <c r="R6" t="n">
-        <v>6845534</v>
+        <v>6845500</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283182</v>
+        <v>123282276</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>79868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488622</v>
+        <v>488614</v>
       </c>
       <c r="R7" t="n">
-        <v>6845865</v>
+        <v>6845651</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282046</v>
+        <v>123281923</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488627</v>
+        <v>488566</v>
       </c>
       <c r="R8" t="n">
-        <v>6845653</v>
+        <v>6845601</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123281905</v>
+        <v>123285070</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>98419</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488550</v>
+        <v>488727</v>
       </c>
       <c r="R9" t="n">
-        <v>6845607</v>
+        <v>6845511</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282126</v>
+        <v>123282646</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>78865</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488580</v>
+        <v>488667</v>
       </c>
       <c r="R10" t="n">
-        <v>6845622</v>
+        <v>6845634</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282094</v>
+        <v>123284651</v>
       </c>
       <c r="B11" t="n">
-        <v>79863</v>
+        <v>79868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,17 +1629,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488580</v>
+        <v>488778</v>
       </c>
       <c r="R11" t="n">
-        <v>6845622</v>
+        <v>6845534</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,11 +1669,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282344</v>
+        <v>123281886</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>79867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488613</v>
+        <v>488542</v>
       </c>
       <c r="R12" t="n">
-        <v>6845644</v>
+        <v>6845601</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123283245</v>
+        <v>123281905</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488616</v>
+        <v>488550</v>
       </c>
       <c r="R13" t="n">
-        <v>6845834</v>
+        <v>6845607</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123282276</v>
+        <v>123283234</v>
       </c>
       <c r="B14" t="n">
-        <v>79863</v>
+        <v>90988</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488614</v>
+        <v>488645</v>
       </c>
       <c r="R14" t="n">
-        <v>6845651</v>
+        <v>6845868</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123282646</v>
+        <v>123282046</v>
       </c>
       <c r="B15" t="n">
-        <v>78860</v>
+        <v>79867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488627</v>
       </c>
       <c r="R15" t="n">
-        <v>6845634</v>
+        <v>6845653</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123285070</v>
+        <v>123282094</v>
       </c>
       <c r="B16" t="n">
-        <v>98313</v>
+        <v>79868</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,38 +2115,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488727</v>
+        <v>488580</v>
       </c>
       <c r="R16" t="n">
-        <v>6845511</v>
+        <v>6845622</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2189,6 +2179,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283234</v>
+        <v>123282126</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>79867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488645</v>
+        <v>488580</v>
       </c>
       <c r="R17" t="n">
-        <v>6845868</v>
+        <v>6845622</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123283290</v>
+        <v>123282344</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,38 +2324,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488669</v>
+        <v>488613</v>
       </c>
       <c r="R18" t="n">
-        <v>6845859</v>
+        <v>6845644</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2393,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123283290</v>
+        <v>123281905</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488669</v>
+        <v>488550</v>
       </c>
       <c r="R2" t="n">
-        <v>6845859</v>
+        <v>6845607</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283182</v>
+        <v>123282344</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488622</v>
+        <v>488613</v>
       </c>
       <c r="R3" t="n">
-        <v>6845865</v>
+        <v>6845644</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123282365</v>
+        <v>123283290</v>
       </c>
       <c r="B4" t="n">
-        <v>79868</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488621</v>
+        <v>488669</v>
       </c>
       <c r="R4" t="n">
-        <v>6845654</v>
+        <v>6845859</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283245</v>
+        <v>123281886</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488616</v>
+        <v>488542</v>
       </c>
       <c r="R5" t="n">
-        <v>6845834</v>
+        <v>6845601</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284387</v>
+        <v>123284651</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488840</v>
+        <v>488778</v>
       </c>
       <c r="R6" t="n">
-        <v>6845500</v>
+        <v>6845534</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282276</v>
+        <v>123282126</v>
       </c>
       <c r="B7" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488614</v>
+        <v>488580</v>
       </c>
       <c r="R7" t="n">
-        <v>6845651</v>
+        <v>6845622</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123281923</v>
+        <v>123282046</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488566</v>
+        <v>488627</v>
       </c>
       <c r="R8" t="n">
-        <v>6845601</v>
+        <v>6845653</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285070</v>
+        <v>123282276</v>
       </c>
       <c r="B9" t="n">
-        <v>98419</v>
+        <v>79870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1406,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488727</v>
+        <v>488614</v>
       </c>
       <c r="R9" t="n">
-        <v>6845511</v>
+        <v>6845651</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282646</v>
+        <v>123282365</v>
       </c>
       <c r="B10" t="n">
-        <v>78865</v>
+        <v>79870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488667</v>
+        <v>488621</v>
       </c>
       <c r="R10" t="n">
-        <v>6845634</v>
+        <v>6845654</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123284651</v>
+        <v>123285070</v>
       </c>
       <c r="B11" t="n">
-        <v>79868</v>
+        <v>98421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488778</v>
+        <v>488727</v>
       </c>
       <c r="R11" t="n">
-        <v>6845534</v>
+        <v>6845511</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123281886</v>
+        <v>123283234</v>
       </c>
       <c r="B12" t="n">
-        <v>79867</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488542</v>
+        <v>488645</v>
       </c>
       <c r="R12" t="n">
-        <v>6845601</v>
+        <v>6845868</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281905</v>
+        <v>123281923</v>
       </c>
       <c r="B13" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488550</v>
+        <v>488566</v>
       </c>
       <c r="R13" t="n">
-        <v>6845607</v>
+        <v>6845601</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123283234</v>
+        <v>123284387</v>
       </c>
       <c r="B14" t="n">
-        <v>90988</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488645</v>
+        <v>488840</v>
       </c>
       <c r="R14" t="n">
-        <v>6845868</v>
+        <v>6845500</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123282046</v>
+        <v>123283245</v>
       </c>
       <c r="B15" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488627</v>
+        <v>488616</v>
       </c>
       <c r="R15" t="n">
-        <v>6845653</v>
+        <v>6845834</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,7 +2111,7 @@
         <v>123282094</v>
       </c>
       <c r="B16" t="n">
-        <v>79868</v>
+        <v>79870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123282126</v>
+        <v>123283182</v>
       </c>
       <c r="B17" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,34 +2231,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488580</v>
+        <v>488622</v>
       </c>
       <c r="R17" t="n">
-        <v>6845622</v>
+        <v>6845865</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282344</v>
+        <v>123282646</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>78867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,38 +2329,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488613</v>
+        <v>488667</v>
       </c>
       <c r="R18" t="n">
-        <v>6845644</v>
+        <v>6845634</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2388,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123281886</v>
+        <v>123284651</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488542</v>
+        <v>488778</v>
       </c>
       <c r="R5" t="n">
-        <v>6845601</v>
+        <v>6845534</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284651</v>
+        <v>123282126</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488778</v>
+        <v>488580</v>
       </c>
       <c r="R6" t="n">
-        <v>6845534</v>
+        <v>6845622</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282126</v>
+        <v>123281886</v>
       </c>
       <c r="B7" t="n">
         <v>79869</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488580</v>
+        <v>488542</v>
       </c>
       <c r="R7" t="n">
-        <v>6845622</v>
+        <v>6845601</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284651</v>
+        <v>123281886</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488778</v>
+        <v>488542</v>
       </c>
       <c r="R5" t="n">
-        <v>6845534</v>
+        <v>6845601</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123282126</v>
+        <v>123284651</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488580</v>
+        <v>488778</v>
       </c>
       <c r="R6" t="n">
-        <v>6845622</v>
+        <v>6845534</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123281886</v>
+        <v>123282126</v>
       </c>
       <c r="B7" t="n">
         <v>79869</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488542</v>
+        <v>488580</v>
       </c>
       <c r="R7" t="n">
-        <v>6845601</v>
+        <v>6845622</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123281905</v>
+        <v>123282365</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488550</v>
+        <v>488621</v>
       </c>
       <c r="R2" t="n">
-        <v>6845607</v>
+        <v>6845654</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123282344</v>
+        <v>123283245</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488613</v>
+        <v>488616</v>
       </c>
       <c r="R3" t="n">
-        <v>6845644</v>
+        <v>6845834</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283290</v>
+        <v>123281905</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488669</v>
+        <v>488550</v>
       </c>
       <c r="R4" t="n">
-        <v>6845859</v>
+        <v>6845607</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123281886</v>
+        <v>123283290</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488542</v>
+        <v>488669</v>
       </c>
       <c r="R5" t="n">
-        <v>6845601</v>
+        <v>6845859</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284651</v>
+        <v>123281886</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488778</v>
+        <v>488542</v>
       </c>
       <c r="R6" t="n">
-        <v>6845534</v>
+        <v>6845601</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282126</v>
+        <v>123282344</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R7" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282046</v>
+        <v>123284651</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488627</v>
+        <v>488778</v>
       </c>
       <c r="R8" t="n">
-        <v>6845653</v>
+        <v>6845534</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123282276</v>
+        <v>123281923</v>
       </c>
       <c r="B9" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488614</v>
+        <v>488566</v>
       </c>
       <c r="R9" t="n">
-        <v>6845651</v>
+        <v>6845601</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282365</v>
+        <v>123282094</v>
       </c>
       <c r="B10" t="n">
         <v>79870</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488621</v>
+        <v>488580</v>
       </c>
       <c r="R10" t="n">
-        <v>6845654</v>
+        <v>6845622</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1572,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,7 +1606,7 @@
         <v>123285070</v>
       </c>
       <c r="B11" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123283234</v>
+        <v>123284387</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488645</v>
+        <v>488840</v>
       </c>
       <c r="R12" t="n">
-        <v>6845868</v>
+        <v>6845500</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281923</v>
+        <v>123282126</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488566</v>
+        <v>488580</v>
       </c>
       <c r="R13" t="n">
-        <v>6845601</v>
+        <v>6845622</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123284387</v>
+        <v>123282276</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,34 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488840</v>
+        <v>488614</v>
       </c>
       <c r="R14" t="n">
-        <v>6845500</v>
+        <v>6845651</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2006,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123283245</v>
+        <v>123283182</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2042,17 +2047,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488616</v>
+        <v>488622</v>
       </c>
       <c r="R15" t="n">
-        <v>6845834</v>
+        <v>6845865</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282094</v>
+        <v>123282646</v>
       </c>
       <c r="B16" t="n">
-        <v>79870</v>
+        <v>78867</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488580</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>6845622</v>
+        <v>6845634</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2184,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283182</v>
+        <v>123283234</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488622</v>
+        <v>488645</v>
       </c>
       <c r="R17" t="n">
-        <v>6845865</v>
+        <v>6845868</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282646</v>
+        <v>123282046</v>
       </c>
       <c r="B18" t="n">
-        <v>78867</v>
+        <v>79869</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,37 +2333,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488667</v>
+        <v>488627</v>
       </c>
       <c r="R18" t="n">
-        <v>6845634</v>
+        <v>6845653</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123282365</v>
+        <v>123284651</v>
       </c>
       <c r="B2" t="n">
         <v>79870</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488621</v>
+        <v>488778</v>
       </c>
       <c r="R2" t="n">
-        <v>6845654</v>
+        <v>6845534</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283245</v>
+        <v>123283182</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488616</v>
+        <v>488622</v>
       </c>
       <c r="R3" t="n">
-        <v>6845834</v>
+        <v>6845865</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123281905</v>
+        <v>123284387</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488550</v>
+        <v>488840</v>
       </c>
       <c r="R4" t="n">
-        <v>6845607</v>
+        <v>6845500</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283290</v>
+        <v>123283234</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488669</v>
+        <v>488645</v>
       </c>
       <c r="R5" t="n">
-        <v>6845859</v>
+        <v>6845868</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123281886</v>
+        <v>123282365</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488542</v>
+        <v>488621</v>
       </c>
       <c r="R6" t="n">
-        <v>6845601</v>
+        <v>6845654</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282344</v>
+        <v>123281923</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488613</v>
+        <v>488566</v>
       </c>
       <c r="R7" t="n">
-        <v>6845644</v>
+        <v>6845601</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123284651</v>
+        <v>123282126</v>
       </c>
       <c r="B8" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488778</v>
+        <v>488580</v>
       </c>
       <c r="R8" t="n">
-        <v>6845534</v>
+        <v>6845622</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123281923</v>
+        <v>123283245</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1430,17 +1425,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488566</v>
+        <v>488616</v>
       </c>
       <c r="R9" t="n">
-        <v>6845601</v>
+        <v>6845834</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123282094</v>
+        <v>123285070</v>
       </c>
       <c r="B10" t="n">
-        <v>79870</v>
+        <v>97996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488580</v>
+        <v>488727</v>
       </c>
       <c r="R10" t="n">
-        <v>6845622</v>
+        <v>6845511</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1572,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123285070</v>
+        <v>123282276</v>
       </c>
       <c r="B11" t="n">
-        <v>97996</v>
+        <v>79870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488727</v>
+        <v>488614</v>
       </c>
       <c r="R11" t="n">
-        <v>6845511</v>
+        <v>6845651</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123284387</v>
+        <v>123282046</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488840</v>
+        <v>488627</v>
       </c>
       <c r="R12" t="n">
-        <v>6845500</v>
+        <v>6845653</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,19 +1785,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123282126</v>
+        <v>123281905</v>
       </c>
       <c r="B13" t="n">
         <v>79869</v>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488580</v>
+        <v>488550</v>
       </c>
       <c r="R13" t="n">
-        <v>6845622</v>
+        <v>6845607</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123282276</v>
+        <v>123283290</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488614</v>
+        <v>488669</v>
       </c>
       <c r="R14" t="n">
-        <v>6845651</v>
+        <v>6845859</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123283182</v>
+        <v>123282646</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488622</v>
+        <v>488667</v>
       </c>
       <c r="R15" t="n">
-        <v>6845865</v>
+        <v>6845634</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282646</v>
+        <v>123282344</v>
       </c>
       <c r="B16" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,38 +2115,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488613</v>
       </c>
       <c r="R16" t="n">
-        <v>6845634</v>
+        <v>6845644</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2189,6 +2179,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283234</v>
+        <v>123282094</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>79870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488645</v>
+        <v>488580</v>
       </c>
       <c r="R17" t="n">
-        <v>6845868</v>
+        <v>6845622</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282046</v>
+        <v>123281886</v>
       </c>
       <c r="B18" t="n">
         <v>79869</v>
@@ -2353,17 +2353,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488627</v>
+        <v>488542</v>
       </c>
       <c r="R18" t="n">
-        <v>6845653</v>
+        <v>6845601</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,12 +2407,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284651</v>
+        <v>123282646</v>
       </c>
       <c r="B2" t="n">
-        <v>79870</v>
+        <v>78867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488778</v>
+        <v>488667</v>
       </c>
       <c r="R2" t="n">
-        <v>6845534</v>
+        <v>6845634</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283182</v>
+        <v>123285070</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488622</v>
+        <v>488727</v>
       </c>
       <c r="R3" t="n">
-        <v>6845865</v>
+        <v>6845511</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123284387</v>
+        <v>123282126</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488840</v>
+        <v>488580</v>
       </c>
       <c r="R4" t="n">
-        <v>6845500</v>
+        <v>6845622</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283234</v>
+        <v>123282276</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>79870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488645</v>
+        <v>488614</v>
       </c>
       <c r="R5" t="n">
-        <v>6845868</v>
+        <v>6845651</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123282365</v>
+        <v>123281923</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488621</v>
+        <v>488566</v>
       </c>
       <c r="R6" t="n">
-        <v>6845654</v>
+        <v>6845601</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123281923</v>
+        <v>123284651</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488566</v>
+        <v>488778</v>
       </c>
       <c r="R7" t="n">
-        <v>6845601</v>
+        <v>6845534</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282126</v>
+        <v>123282344</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488580</v>
+        <v>488613</v>
       </c>
       <c r="R8" t="n">
-        <v>6845622</v>
+        <v>6845644</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123283245</v>
+        <v>123284387</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1425,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488616</v>
+        <v>488840</v>
       </c>
       <c r="R9" t="n">
-        <v>6845834</v>
+        <v>6845500</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285070</v>
+        <v>123283182</v>
       </c>
       <c r="B10" t="n">
-        <v>97996</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488727</v>
+        <v>488622</v>
       </c>
       <c r="R10" t="n">
-        <v>6845511</v>
+        <v>6845865</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282276</v>
+        <v>123281905</v>
       </c>
       <c r="B11" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488614</v>
+        <v>488550</v>
       </c>
       <c r="R11" t="n">
-        <v>6845651</v>
+        <v>6845607</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282046</v>
+        <v>123282094</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1716,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488627</v>
+        <v>488580</v>
       </c>
       <c r="R12" t="n">
-        <v>6845653</v>
+        <v>6845622</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123281905</v>
+        <v>123282365</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488550</v>
+        <v>488621</v>
       </c>
       <c r="R13" t="n">
-        <v>6845607</v>
+        <v>6845654</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123283290</v>
+        <v>123281886</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,34 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488669</v>
+        <v>488542</v>
       </c>
       <c r="R14" t="n">
-        <v>6845859</v>
+        <v>6845601</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123282646</v>
+        <v>123283245</v>
       </c>
       <c r="B15" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488616</v>
       </c>
       <c r="R15" t="n">
-        <v>6845634</v>
+        <v>6845834</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123282344</v>
+        <v>123283234</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,38 +2125,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488613</v>
+        <v>488645</v>
       </c>
       <c r="R16" t="n">
-        <v>6845644</v>
+        <v>6845868</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2179,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123282094</v>
+        <v>123282046</v>
       </c>
       <c r="B17" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,37 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488580</v>
+        <v>488627</v>
       </c>
       <c r="R17" t="n">
-        <v>6845622</v>
+        <v>6845653</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123281886</v>
+        <v>123283290</v>
       </c>
       <c r="B18" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488542</v>
+        <v>488669</v>
       </c>
       <c r="R18" t="n">
-        <v>6845601</v>
+        <v>6845859</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123282646</v>
+        <v>123284651</v>
       </c>
       <c r="B2" t="n">
-        <v>78867</v>
+        <v>79870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488667</v>
+        <v>488778</v>
       </c>
       <c r="R2" t="n">
-        <v>6845634</v>
+        <v>6845534</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123285070</v>
+        <v>123283234</v>
       </c>
       <c r="B3" t="n">
-        <v>97996</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488727</v>
+        <v>488645</v>
       </c>
       <c r="R3" t="n">
-        <v>6845511</v>
+        <v>6845868</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123282126</v>
+        <v>123283290</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488580</v>
+        <v>488669</v>
       </c>
       <c r="R4" t="n">
-        <v>6845622</v>
+        <v>6845859</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123282276</v>
+        <v>123284387</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488614</v>
+        <v>488840</v>
       </c>
       <c r="R5" t="n">
-        <v>6845651</v>
+        <v>6845500</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123281923</v>
+        <v>123282094</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488566</v>
+        <v>488580</v>
       </c>
       <c r="R6" t="n">
-        <v>6845601</v>
+        <v>6845622</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284651</v>
+        <v>123282046</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488778</v>
+        <v>488627</v>
       </c>
       <c r="R7" t="n">
-        <v>6845534</v>
+        <v>6845653</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123282344</v>
+        <v>123283182</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488613</v>
+        <v>488622</v>
       </c>
       <c r="R8" t="n">
-        <v>6845644</v>
+        <v>6845865</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123284387</v>
+        <v>123282365</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488840</v>
+        <v>488621</v>
       </c>
       <c r="R9" t="n">
-        <v>6845500</v>
+        <v>6845654</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123283182</v>
+        <v>123281905</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488622</v>
+        <v>488550</v>
       </c>
       <c r="R10" t="n">
-        <v>6845865</v>
+        <v>6845607</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123281905</v>
+        <v>123282344</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488550</v>
+        <v>488613</v>
       </c>
       <c r="R11" t="n">
-        <v>6845607</v>
+        <v>6845644</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282094</v>
+        <v>123282276</v>
       </c>
       <c r="B12" t="n">
         <v>79870</v>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488580</v>
+        <v>488614</v>
       </c>
       <c r="R12" t="n">
-        <v>6845622</v>
+        <v>6845651</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123282365</v>
+        <v>123282126</v>
       </c>
       <c r="B13" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488621</v>
+        <v>488580</v>
       </c>
       <c r="R13" t="n">
-        <v>6845654</v>
+        <v>6845622</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123283245</v>
+        <v>123281923</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2047,17 +2047,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488616</v>
+        <v>488566</v>
       </c>
       <c r="R15" t="n">
-        <v>6845834</v>
+        <v>6845601</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123283234</v>
+        <v>123285070</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>97996</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488645</v>
+        <v>488727</v>
       </c>
       <c r="R16" t="n">
-        <v>6845868</v>
+        <v>6845511</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123282046</v>
+        <v>123283245</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488627</v>
+        <v>488616</v>
       </c>
       <c r="R17" t="n">
-        <v>6845653</v>
+        <v>6845834</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123283290</v>
+        <v>123282646</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488669</v>
+        <v>488667</v>
       </c>
       <c r="R18" t="n">
-        <v>6845859</v>
+        <v>6845634</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284651</v>
+        <v>123282646</v>
       </c>
       <c r="B2" t="n">
-        <v>79870</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488778</v>
+        <v>488667</v>
       </c>
       <c r="R2" t="n">
-        <v>6845534</v>
+        <v>6845634</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>123283234</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283290</v>
+        <v>123282094</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488669</v>
+        <v>488580</v>
       </c>
       <c r="R4" t="n">
-        <v>6845859</v>
+        <v>6845622</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284387</v>
+        <v>123282276</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488840</v>
+        <v>488614</v>
       </c>
       <c r="R5" t="n">
-        <v>6845500</v>
+        <v>6845651</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123282094</v>
+        <v>123282365</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488580</v>
+        <v>488621</v>
       </c>
       <c r="R6" t="n">
-        <v>6845622</v>
+        <v>6845654</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tätt beklädd av skrovellav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123282046</v>
+        <v>123284651</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1176,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488627</v>
+        <v>488778</v>
       </c>
       <c r="R7" t="n">
-        <v>6845653</v>
+        <v>6845534</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,31 +1250,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283182</v>
+        <v>123281923</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1328,14 +1293,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488622</v>
+        <v>488566</v>
       </c>
       <c r="R8" t="n">
-        <v>6845865</v>
+        <v>6845601</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,53 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123282365</v>
+        <v>123282363</v>
       </c>
       <c r="B9" t="n">
-        <v>79870</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488621</v>
+        <v>488620</v>
       </c>
       <c r="R9" t="n">
-        <v>6845654</v>
+        <v>6845668</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,62 +1444,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123281905</v>
+        <v>123283182</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488550</v>
+        <v>488622</v>
       </c>
       <c r="R10" t="n">
-        <v>6845607</v>
+        <v>6845865</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123282344</v>
+        <v>123283245</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,37 +1564,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488613</v>
+        <v>488616</v>
       </c>
       <c r="R11" t="n">
-        <v>6845644</v>
+        <v>6845834</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,11 +1624,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,62 +1638,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123282276</v>
+        <v>123283290</v>
       </c>
       <c r="B12" t="n">
-        <v>79870</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488614</v>
+        <v>488669</v>
       </c>
       <c r="R12" t="n">
-        <v>6845651</v>
+        <v>6845859</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,50 +1747,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123282126</v>
+        <v>123284387</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelmyran, Kringelmyran, Dlr</t>
+          <t>Långtjärnen, Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488580</v>
+        <v>488840</v>
       </c>
       <c r="R13" t="n">
-        <v>6845622</v>
+        <v>6845500</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1912,12 +1847,7 @@
         <v>123281886</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2011,15 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123281923</v>
+        <v>123281905</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488566</v>
+        <v>488550</v>
       </c>
       <c r="R15" t="n">
-        <v>6845601</v>
+        <v>6845607</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2113,53 +2038,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123285070</v>
+        <v>123282046</v>
       </c>
       <c r="B16" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Dlr</t>
+          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488727</v>
+        <v>488627</v>
       </c>
       <c r="R16" t="n">
-        <v>6845511</v>
+        <v>6845653</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,27 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123283245</v>
+        <v>123282126</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,37 +2146,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartåvallens gammelskog, Svartåvallens gammelskog, Dlr</t>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488616</v>
+        <v>488580</v>
       </c>
       <c r="R17" t="n">
-        <v>6845834</v>
+        <v>6845622</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,49 +2220,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123282646</v>
+        <v>123285070</v>
       </c>
       <c r="B18" t="n">
-        <v>78867</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488667</v>
+        <v>488727</v>
       </c>
       <c r="R18" t="n">
-        <v>6845634</v>
+        <v>6845511</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2416,6 +2326,108 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123282344</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kringelmyran, Kringelmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488613</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6845644</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nio vissnade blomstänglar och en tjock matta av rosetter.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42763-2021 artfynd.xlsx
+++ b/artfynd/A 42763-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282094</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282365</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123281923</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282363</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283182</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283245</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283290</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284387</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123281886</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123281905</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282046</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282126</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123285070</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,8 +2518,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123282344</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>